--- a/te.xlsx
+++ b/te.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B109"/>
+  <dimension ref="A1:B108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -435,7 +435,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7092</v>
+        <v>727</v>
       </c>
     </row>
     <row r="3">
@@ -445,17 +445,17 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>601</v>
+        <v>494</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Turkey</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>488</v>
+        <v>359</v>
       </c>
     </row>
     <row r="5">
@@ -465,7 +465,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>353</v>
+        <v>346</v>
       </c>
     </row>
     <row r="6">
@@ -475,17 +475,17 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>307</v>
+        <v>328</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Turkey</t>
+          <t>China</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>284</v>
+        <v>324</v>
       </c>
     </row>
     <row r="8">
@@ -495,67 +495,67 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>277</v>
+        <v>268</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>242</v>
+        <v>245</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>France</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>200</v>
+        <v>235</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>197</v>
+        <v>211</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>194</v>
+        <v>197</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>India</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>180</v>
+        <v>195</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>United Arab Emirates</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>161</v>
+        <v>170</v>
       </c>
     </row>
     <row r="15">
@@ -565,7 +565,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>159</v>
+        <v>145</v>
       </c>
     </row>
     <row r="16">
@@ -575,43 +575,43 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>154</v>
+        <v>133</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Kingdom of the Netherlands</t>
+          <t>Republic of Korea</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>128</v>
+        <v>125</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>Kingdom of the Netherlands</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>110</v>
+        <v>122</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>105</v>
+        <v>109</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -621,311 +621,311 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Qatar</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>72</v>
+        <v>93</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Taiwan</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>72</v>
+        <v>84</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Hungary</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>68</v>
+        <v>80</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Qatar</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>68</v>
+        <v>79</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Republic of Korea</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>55</v>
+        <v>77</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Greece</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>53</v>
+        <v>71</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Hungary</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>53</v>
+        <v>67</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Czech Republic</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>53</v>
+        <v>64</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Malaysia</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>49</v>
+        <v>63</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Greece</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>49</v>
+        <v>61</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Russian Federation</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>45</v>
+        <v>52</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Israel</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>Indonesia</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Czech Republic</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Taiwan</t>
+          <t>Israel</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Thailand</t>
+          <t>Latvia</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Luxembourg</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Latvia</t>
+          <t>Romania</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Malaysia</t>
+          <t>Denmark</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Russian Federation</t>
+          <t>Morocco</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Luxembourg</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>Chile</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Panama</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Panama</t>
+          <t>Bulgaria</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Romania</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="52">
@@ -935,43 +935,43 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>Saudi Arabia</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Viet Nam</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Ethiopia</t>
+          <t>Viet Nam</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Oman</t>
+          <t>Bangladesh</t>
         </is>
       </c>
       <c r="B56" t="n">
@@ -981,57 +981,57 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Croatia</t>
+          <t>Uzbekistan</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>San Marino</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>San Marino</t>
+          <t>Croatia</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Serbia</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Bangladesh</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Pakistan</t>
+          <t>Ethiopia</t>
         </is>
       </c>
       <c r="B62" t="n">
@@ -1041,27 +1041,27 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Slovakia</t>
+          <t>Pakistan</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Kuwait</t>
+          <t>Tunisia</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Guatemala</t>
+          <t>Slovakia</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -1071,17 +1071,17 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Serbia</t>
+          <t>Estonia</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Bahrain</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -1091,27 +1091,27 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Estonia</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="B70" t="n">
@@ -1121,77 +1121,77 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Cyprus</t>
+          <t>Bahrain</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Algeria</t>
+          <t>Ukraine</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Dominican Republic</t>
+          <t>Sri Lanka</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Tunisia</t>
+          <t>Kuwait</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Indonesia</t>
+          <t>Lebanon</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Slovenia</t>
+          <t>Myanmar</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Costa Rica</t>
+          <t>Republic of Moldova</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Myanmar</t>
+          <t>Georgia</t>
         </is>
       </c>
       <c r="B78" t="n">
@@ -1201,27 +1201,27 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Venezuela</t>
+          <t>Maldives</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Sri Lanka</t>
+          <t>Slovenia</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Uzbekistan</t>
+          <t>Belarus</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -1231,7 +1231,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Lebanon</t>
+          <t>Oman</t>
         </is>
       </c>
       <c r="B82" t="n">
@@ -1241,77 +1241,77 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Republic of Moldova</t>
+          <t>Nepal</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Georgia</t>
+          <t>Cyprus</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Turkmenistan</t>
+          <t>Cambodia</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Nepal</t>
+          <t>Iraq</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Ukraine</t>
+          <t>Kazakhstan</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Belarus</t>
+          <t>Afghanistan</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Cambodia</t>
+          <t>Azerbaijan</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Iraq</t>
+          <t>Islamic Republic of Iran</t>
         </is>
       </c>
       <c r="B90" t="n">
@@ -1321,7 +1321,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Brunei Darussalam</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -1331,7 +1331,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Trinidad and Tobago</t>
+          <t>Montenegro</t>
         </is>
       </c>
       <c r="B92" t="n">
@@ -1341,7 +1341,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Islamic Republic of Iran</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -1351,7 +1351,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Paraguay</t>
+          <t>Turkmenistan</t>
         </is>
       </c>
       <c r="B94" t="n">
@@ -1361,17 +1361,17 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Mauritius</t>
+          <t>Syrian Arab Republic</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Syrian Arab Republic</t>
+          <t>Libyan Arab Jamahiriya</t>
         </is>
       </c>
       <c r="B96" t="n">
@@ -1381,7 +1381,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Libyan Arab Jamahiriya</t>
+          <t>Brunei Darussalam</t>
         </is>
       </c>
       <c r="B97" t="n">
@@ -1391,7 +1391,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>United Republic of Tanzania</t>
+          <t>Trinidad and Tobago</t>
         </is>
       </c>
       <c r="B98" t="n">
@@ -1401,7 +1401,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina</t>
+          <t>Angola</t>
         </is>
       </c>
       <c r="B99" t="n">
@@ -1411,7 +1411,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Nigeria</t>
+          <t>Bhutan</t>
         </is>
       </c>
       <c r="B100" t="n">
@@ -1421,7 +1421,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Angola</t>
+          <t>Zambia</t>
         </is>
       </c>
       <c r="B101" t="n">
@@ -1431,7 +1431,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Suriname</t>
+          <t>Mauritius</t>
         </is>
       </c>
       <c r="B102" t="n">
@@ -1441,7 +1441,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Fiji</t>
+          <t>Ecuador</t>
         </is>
       </c>
       <c r="B103" t="n">
@@ -1451,7 +1451,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Sudan</t>
+          <t>Seychelles</t>
         </is>
       </c>
       <c r="B104" t="n">
@@ -1461,7 +1461,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Bhutan</t>
+          <t>Côte d'Ivoire</t>
         </is>
       </c>
       <c r="B105" t="n">
@@ -1471,7 +1471,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Azerbaijan</t>
+          <t>Rwanda</t>
         </is>
       </c>
       <c r="B106" t="n">
@@ -1479,11 +1479,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>Bahamas</t>
-        </is>
-      </c>
+      <c r="A107" t="inlineStr"/>
       <c r="B107" t="n">
         <v>1</v>
       </c>
@@ -1491,20 +1487,10 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Rwanda</t>
+          <t>Armenia</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>Bolivia</t>
-        </is>
-      </c>
-      <c r="B109" t="n">
         <v>1</v>
       </c>
     </row>

--- a/te.xlsx
+++ b/te.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B108"/>
+  <dimension ref="A1:B103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -435,127 +435,127 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>727</v>
+        <v>7923</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>494</v>
+        <v>558</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Turkey</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>359</v>
+        <v>407</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Ireland</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>346</v>
+        <v>305</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>Turkey</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>328</v>
+        <v>289</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Malta</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>324</v>
+        <v>252</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>268</v>
+        <v>230</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>245</v>
+        <v>172</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>235</v>
+        <v>168</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>France</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>211</v>
+        <v>149</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>Austria</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>197</v>
+        <v>139</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>China</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>195</v>
+        <v>125</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>170</v>
+        <v>119</v>
       </c>
     </row>
     <row r="15">
@@ -565,97 +565,97 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>145</v>
+        <v>107</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>United Arab Emirates</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>133</v>
+        <v>102</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Republic of Korea</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>125</v>
+        <v>88</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Kingdom of the Netherlands</t>
+          <t>India</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>122</v>
+        <v>84</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>109</v>
+        <v>73</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Qatar</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>101</v>
+        <v>70</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Qatar</t>
+          <t>Kingdom of the Netherlands</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>93</v>
+        <v>69</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Taiwan</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>84</v>
+        <v>68</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Republic of Korea</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>80</v>
+        <v>63</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Hungary</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>79</v>
+        <v>61</v>
       </c>
     </row>
     <row r="25">
@@ -665,127 +665,127 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>77</v>
+        <v>57</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Thailand</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>71</v>
+        <v>56</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Hungary</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>67</v>
+        <v>51</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Greece</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>64</v>
+        <v>46</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Malaysia</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>63</v>
+        <v>45</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Greece</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>61</v>
+        <v>41</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>53</v>
+        <v>41</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Russian Federation</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>52</v>
+        <v>41</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Taiwan</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Morocco</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Chile</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>44</v>
+        <v>35</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Indonesia</t>
+          <t>Latvia</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>42</v>
+        <v>31</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Czech Republic</t>
+          <t>Denmark</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>42</v>
+        <v>28</v>
       </c>
     </row>
     <row r="38">
@@ -795,147 +795,147 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>39</v>
+        <v>28</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>Malaysia</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>38</v>
+        <v>27</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>Russian Federation</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Latvia</t>
+          <t>Viet Nam</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>34</v>
+        <v>25</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>33</v>
+        <v>22</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Romania</t>
+          <t>Bulgaria</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>32</v>
+        <v>21</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>Luxembourg</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>31</v>
+        <v>21</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Luxembourg</t>
+          <t>Czech Republic</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Panama</t>
+          <t>Lithuania</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>Guatemala</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Panama</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Lithuania</t>
+          <t>Tunisia</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
     </row>
     <row r="53">
@@ -945,83 +945,83 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Viet Nam</t>
+          <t>Romania</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Bangladesh</t>
+          <t>San Marino</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Uzbekistan</t>
+          <t>Croatia</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>San Marino</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Croatia</t>
+          <t>Bahrain</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Serbia</t>
+          <t>Ethiopia</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -1031,11 +1031,11 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Ethiopia</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="63">
@@ -1045,203 +1045,203 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Tunisia</t>
+          <t>Indonesia</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Slovakia</t>
+          <t>Estonia</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Estonia</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>Serbia</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Uzbekistan</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Ukraine</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Algeria</t>
+          <t>Oman</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Bahrain</t>
+          <t>Bangladesh</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Ukraine</t>
+          <t>Republic of Moldova</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Sri Lanka</t>
+          <t>Georgia</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Kuwait</t>
+          <t>Nepal</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Lebanon</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Myanmar</t>
+          <t>Sri Lanka</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Republic of Moldova</t>
+          <t>Kuwait</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Georgia</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Maldives</t>
+          <t>Brunei Darussalam</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Slovenia</t>
+          <t>Cyprus</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Belarus</t>
+          <t>Kazakhstan</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Oman</t>
+          <t>Azerbaijan</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Nepal</t>
+          <t>Afghanistan</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -1251,27 +1251,27 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Cyprus</t>
+          <t>Slovakia</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Cambodia</t>
+          <t>Slovenia</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Iraq</t>
+          <t>Lebanon</t>
         </is>
       </c>
       <c r="B86" t="n">
@@ -1281,7 +1281,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Kazakhstan</t>
+          <t>Uruguay</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -1291,7 +1291,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Afghanistan</t>
+          <t>Angola</t>
         </is>
       </c>
       <c r="B88" t="n">
@@ -1301,7 +1301,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Azerbaijan</t>
+          <t>Islamic Republic of Iran</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -1311,7 +1311,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Islamic Republic of Iran</t>
+          <t>Venezuela</t>
         </is>
       </c>
       <c r="B90" t="n">
@@ -1321,7 +1321,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Dominican Republic</t>
+          <t>Cambodia</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -1331,7 +1331,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Montenegro</t>
+          <t>Costa Rica</t>
         </is>
       </c>
       <c r="B92" t="n">
@@ -1341,7 +1341,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Bolivia</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -1351,17 +1351,17 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Turkmenistan</t>
+          <t>Iraq</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Syrian Arab Republic</t>
+          <t>Uganda</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -1371,7 +1371,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Libyan Arab Jamahiriya</t>
+          <t>Vanuatu</t>
         </is>
       </c>
       <c r="B96" t="n">
@@ -1381,7 +1381,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Brunei Darussalam</t>
+          <t>Trinidad and Tobago</t>
         </is>
       </c>
       <c r="B97" t="n">
@@ -1391,7 +1391,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Trinidad and Tobago</t>
+          <t>Myanmar</t>
         </is>
       </c>
       <c r="B98" t="n">
@@ -1401,7 +1401,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Angola</t>
+          <t>Belarus</t>
         </is>
       </c>
       <c r="B99" t="n">
@@ -1411,7 +1411,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Bhutan</t>
+          <t>Syrian Arab Republic</t>
         </is>
       </c>
       <c r="B100" t="n">
@@ -1421,7 +1421,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Zambia</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="B101" t="n">
@@ -1431,7 +1431,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Mauritius</t>
+          <t>Paraguay</t>
         </is>
       </c>
       <c r="B102" t="n">
@@ -1441,56 +1441,10 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Ecuador</t>
+          <t>Cape Verde</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>Seychelles</t>
-        </is>
-      </c>
-      <c r="B104" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>Côte d'Ivoire</t>
-        </is>
-      </c>
-      <c r="B105" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>Rwanda</t>
-        </is>
-      </c>
-      <c r="B106" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr"/>
-      <c r="B107" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>Armenia</t>
-        </is>
-      </c>
-      <c r="B108" t="n">
         <v>1</v>
       </c>
     </row>
